--- a/public/templates/screen_template.xlsx
+++ b/public/templates/screen_template.xlsx
@@ -4,8 +4,9 @@
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
     <sheet name="메타정보" sheetId="1" r:id="rId1"/>
-    <sheet name="데이터" sheetId="2" r:id="rId2"/>
-    <sheet name="가이드" sheetId="3" r:id="rId3"/>
+    <sheet name="그리드컬럼" sheetId="2" r:id="rId2"/>
+    <sheet name="샘플데이터" sheetId="3" r:id="rId3"/>
+    <sheet name="가이드" sheetId="4" r:id="rId4"/>
   </sheets>
 </workbook>
 </file>
@@ -399,196 +400,76 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:B5"/>
   <cols>
-    <col min="1" max="1" width="20.83203125" customWidth="1"/>
-    <col min="2" max="2" width="30.83203125" customWidth="1"/>
-    <col min="3" max="3" width="40.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>화면 정의 템플릿</v>
+        <v>화면정의서</v>
+      </c>
+      <c r="B1" t="str">
+        <v/>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>화면명</v>
+      </c>
+      <c r="B2" t="str">
         <v/>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>항목</v>
+        <v>화면명(영문)</v>
       </c>
       <c r="B3" t="str">
-        <v>값</v>
-      </c>
-      <c r="C3" t="str">
-        <v>설명</v>
+        <v/>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>화면명(한글)</v>
+        <v>테이블명</v>
       </c>
       <c r="B4" t="str">
         <v/>
-      </c>
-      <c r="C4" t="str">
-        <v>예: 품목별 재고현황</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="str">
-        <v>화면명(영문)</v>
+        <v>옵션</v>
       </c>
       <c r="B5" t="str">
         <v/>
-      </c>
-      <c r="C5" t="str">
-        <v>예: ItemStockStatus</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>테이블명</v>
-      </c>
-      <c r="B6" t="str">
-        <v/>
-      </c>
-      <c r="C6" t="str">
-        <v>예: TB_ITEM_STOCK (DB 테이블명)</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v>설명</v>
-      </c>
-      <c r="B7" t="str">
-        <v/>
-      </c>
-      <c r="C7" t="str">
-        <v>화면에 대한 설명</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="str">
-        <v>조회조건 정의</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="str">
-        <v>조건명</v>
-      </c>
-      <c r="B10" t="str">
-        <v>DB컬럼</v>
-      </c>
-      <c r="C10" t="str">
-        <v>타입</v>
-      </c>
-      <c r="D10" t="str">
-        <v>기본값</v>
-      </c>
-      <c r="E10" t="str">
-        <v>필수여부</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="str">
-        <v>기준일자</v>
-      </c>
-      <c r="B11" t="str">
-        <v>BASE_DATE</v>
-      </c>
-      <c r="C11" t="str">
-        <v>date</v>
-      </c>
-      <c r="D11" t="str">
-        <v/>
-      </c>
-      <c r="E11" t="str">
-        <v>Y</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="str">
-        <v>품목코드</v>
-      </c>
-      <c r="B12" t="str">
-        <v>ITEM_CD</v>
-      </c>
-      <c r="C12" t="str">
-        <v>text</v>
-      </c>
-      <c r="D12" t="str">
-        <v/>
-      </c>
-      <c r="E12" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="str">
-        <v>품목명</v>
-      </c>
-      <c r="B13" t="str">
-        <v>ITEM_NM</v>
-      </c>
-      <c r="C13" t="str">
-        <v>text</v>
-      </c>
-      <c r="D13" t="str">
-        <v/>
-      </c>
-      <c r="E13" t="str">
-        <v>N</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="str">
-        <v>창고코드</v>
-      </c>
-      <c r="B14" t="str">
-        <v>WH_CD</v>
-      </c>
-      <c r="C14" t="str">
-        <v>combo</v>
-      </c>
-      <c r="D14" t="str">
-        <v/>
-      </c>
-      <c r="E14" t="str">
-        <v>N</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E14"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:B5"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:M4"/>
   <cols>
     <col min="1" max="1" width="12.83203125" customWidth="1"/>
     <col min="2" max="2" width="15.83203125" customWidth="1"/>
     <col min="3" max="3" width="12.83203125" customWidth="1"/>
     <col min="4" max="4" width="8.83203125" customWidth="1"/>
     <col min="5" max="5" width="10.83203125" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="15.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -598,184 +479,311 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v/>
+        <v>품목코드</v>
+      </c>
+      <c r="B2" t="str">
+        <v>품목명</v>
+      </c>
+      <c r="C2" t="str">
+        <v>규격</v>
+      </c>
+      <c r="D2" t="str">
+        <v>단위</v>
+      </c>
+      <c r="E2" t="str">
+        <v>창고</v>
+      </c>
+      <c r="F2" t="str">
+        <v>기초</v>
+      </c>
+      <c r="H2" t="str">
+        <v>입고</v>
+      </c>
+      <c r="J2" t="str">
+        <v>출고</v>
+      </c>
+      <c r="L2" t="str">
+        <v>기말</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="str">
-        <v>품목코드</v>
-      </c>
-      <c r="B3" t="str">
-        <v>품목명</v>
-      </c>
-      <c r="C3" t="str">
-        <v>규격</v>
-      </c>
-      <c r="D3" t="str">
-        <v>단위</v>
-      </c>
-      <c r="E3" t="str">
-        <v>창고</v>
-      </c>
       <c r="F3" t="str">
-        <v>전일재고</v>
+        <v>수량</v>
       </c>
       <c r="G3" t="str">
-        <v>입고수량</v>
+        <v>금액</v>
       </c>
       <c r="H3" t="str">
-        <v>출고수량</v>
+        <v>수량</v>
       </c>
       <c r="I3" t="str">
-        <v>현재고</v>
+        <v>금액</v>
       </c>
       <c r="J3" t="str">
-        <v>비고</v>
+        <v>수량</v>
+      </c>
+      <c r="K3" t="str">
+        <v>금액</v>
+      </c>
+      <c r="L3" t="str">
+        <v>수량</v>
+      </c>
+      <c r="M3" t="str">
+        <v>금액</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>ITEM001</v>
+        <v>합계</v>
       </c>
       <c r="B4" t="str">
-        <v>원자재A</v>
+        <v/>
       </c>
       <c r="C4" t="str">
-        <v>100x50</v>
+        <v/>
       </c>
       <c r="D4" t="str">
-        <v>EA</v>
+        <v/>
       </c>
       <c r="E4" t="str">
-        <v>창고1</v>
-      </c>
-      <c r="F4">
-        <v>1000</v>
-      </c>
-      <c r="G4">
-        <v>500</v>
-      </c>
-      <c r="H4">
-        <v>300</v>
-      </c>
-      <c r="I4">
-        <v>1200</v>
+        <v/>
+      </c>
+      <c r="F4" t="str">
+        <v/>
+      </c>
+      <c r="G4" t="str">
+        <v/>
+      </c>
+      <c r="H4" t="str">
+        <v/>
+      </c>
+      <c r="I4" t="str">
+        <v/>
       </c>
       <c r="J4" t="str">
         <v/>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="str">
-        <v>ITEM002</v>
-      </c>
-      <c r="B5" t="str">
-        <v>원자재B</v>
-      </c>
-      <c r="C5" t="str">
-        <v>200x100</v>
-      </c>
-      <c r="D5" t="str">
-        <v>KG</v>
-      </c>
-      <c r="E5" t="str">
-        <v>창고1</v>
-      </c>
-      <c r="F5">
-        <v>500</v>
-      </c>
-      <c r="G5">
-        <v>200</v>
-      </c>
-      <c r="H5">
-        <v>150</v>
-      </c>
-      <c r="I5">
-        <v>550</v>
-      </c>
-      <c r="J5" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="str">
-        <v>ITEM003</v>
-      </c>
-      <c r="B6" t="str">
-        <v>부품C</v>
-      </c>
-      <c r="C6" t="str">
-        <v>50x30</v>
-      </c>
-      <c r="D6" t="str">
-        <v>EA</v>
-      </c>
-      <c r="E6" t="str">
-        <v>창고2</v>
-      </c>
-      <c r="F6">
-        <v>2000</v>
-      </c>
-      <c r="G6">
-        <v>800</v>
-      </c>
-      <c r="H6">
-        <v>600</v>
-      </c>
-      <c r="I6">
-        <v>2200</v>
-      </c>
-      <c r="J6" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="str">
-        <v/>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="str">
-        <v>합계</v>
-      </c>
-      <c r="B8" t="str">
-        <v/>
-      </c>
-      <c r="C8" t="str">
-        <v/>
-      </c>
-      <c r="D8" t="str">
-        <v/>
-      </c>
-      <c r="E8" t="str">
-        <v/>
-      </c>
-      <c r="F8">
-        <v>3500</v>
-      </c>
-      <c r="G8">
-        <v>1500</v>
-      </c>
-      <c r="H8">
-        <v>1050</v>
-      </c>
-      <c r="I8">
-        <v>3950</v>
-      </c>
-      <c r="J8" t="str">
+      <c r="K4" t="str">
+        <v/>
+      </c>
+      <c r="L4" t="str">
+        <v/>
+      </c>
+      <c r="M4" t="str">
         <v/>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="J2:K2"/>
+    <mergeCell ref="L2:M2"/>
+  </mergeCells>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:M4"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A24"/>
+  <dimension ref="A1:M5"/>
+  <cols>
+    <col min="1" max="1" width="12.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="3" max="3" width="12.83203125" customWidth="1"/>
+    <col min="4" max="4" width="8.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" customWidth="1"/>
+    <col min="8" max="8" width="10.83203125" customWidth="1"/>
+    <col min="9" max="9" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="10.83203125" customWidth="1"/>
+    <col min="11" max="11" width="12.83203125" customWidth="1"/>
+    <col min="12" max="12" width="10.83203125" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="str">
+        <v>샘플 데이터</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="str">
+        <v>품목코드</v>
+      </c>
+      <c r="B2" t="str">
+        <v>품목명</v>
+      </c>
+      <c r="C2" t="str">
+        <v>규격</v>
+      </c>
+      <c r="D2" t="str">
+        <v>단위</v>
+      </c>
+      <c r="E2" t="str">
+        <v>창고</v>
+      </c>
+      <c r="F2" t="str">
+        <v>기초수량</v>
+      </c>
+      <c r="G2" t="str">
+        <v>기초금액</v>
+      </c>
+      <c r="H2" t="str">
+        <v>입고수량</v>
+      </c>
+      <c r="I2" t="str">
+        <v>입고금액</v>
+      </c>
+      <c r="J2" t="str">
+        <v>출고수량</v>
+      </c>
+      <c r="K2" t="str">
+        <v>출고금액</v>
+      </c>
+      <c r="L2" t="str">
+        <v>기말수량</v>
+      </c>
+      <c r="M2" t="str">
+        <v>기말금액</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="str">
+        <v>ITEM001</v>
+      </c>
+      <c r="B3" t="str">
+        <v>원자재A</v>
+      </c>
+      <c r="C3" t="str">
+        <v>100x50</v>
+      </c>
+      <c r="D3" t="str">
+        <v>EA</v>
+      </c>
+      <c r="E3" t="str">
+        <v>창고1</v>
+      </c>
+      <c r="F3">
+        <v>1000</v>
+      </c>
+      <c r="G3">
+        <v>5000000</v>
+      </c>
+      <c r="H3">
+        <v>500</v>
+      </c>
+      <c r="I3">
+        <v>2500000</v>
+      </c>
+      <c r="J3">
+        <v>300</v>
+      </c>
+      <c r="K3">
+        <v>1500000</v>
+      </c>
+      <c r="L3">
+        <v>1200</v>
+      </c>
+      <c r="M3">
+        <v>6000000</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="str">
+        <v>ITEM002</v>
+      </c>
+      <c r="B4" t="str">
+        <v>원자재B</v>
+      </c>
+      <c r="C4" t="str">
+        <v>200x100</v>
+      </c>
+      <c r="D4" t="str">
+        <v>KG</v>
+      </c>
+      <c r="E4" t="str">
+        <v>창고1</v>
+      </c>
+      <c r="F4">
+        <v>500</v>
+      </c>
+      <c r="G4">
+        <v>2000000</v>
+      </c>
+      <c r="H4">
+        <v>200</v>
+      </c>
+      <c r="I4">
+        <v>800000</v>
+      </c>
+      <c r="J4">
+        <v>150</v>
+      </c>
+      <c r="K4">
+        <v>600000</v>
+      </c>
+      <c r="L4">
+        <v>550</v>
+      </c>
+      <c r="M4">
+        <v>2200000</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="str">
+        <v>ITEM003</v>
+      </c>
+      <c r="B5" t="str">
+        <v>부품C</v>
+      </c>
+      <c r="C5" t="str">
+        <v>50x30</v>
+      </c>
+      <c r="D5" t="str">
+        <v>EA</v>
+      </c>
+      <c r="E5" t="str">
+        <v>창고2</v>
+      </c>
+      <c r="F5">
+        <v>2000</v>
+      </c>
+      <c r="G5">
+        <v>3000000</v>
+      </c>
+      <c r="H5">
+        <v>800</v>
+      </c>
+      <c r="I5">
+        <v>1200000</v>
+      </c>
+      <c r="J5">
+        <v>600</v>
+      </c>
+      <c r="K5">
+        <v>900000</v>
+      </c>
+      <c r="L5">
+        <v>2200</v>
+      </c>
+      <c r="M5">
+        <v>3300000</v>
+      </c>
+    </row>
+  </sheetData>
+  <ignoredErrors>
+    <ignoredError numberStoredAsText="1" sqref="A1:M5"/>
+  </ignoredErrors>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:A33"/>
   <cols>
     <col min="1" max="1" width="60.83203125" customWidth="1"/>
   </cols>
@@ -797,7 +805,7 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v xml:space="preserve">   - 화면명(한글): 화면 상단에 표시될 제목</v>
+        <v xml:space="preserve">   - 화면명: 화면 상단에 표시될 제목</v>
       </c>
     </row>
     <row r="5">
@@ -812,7 +820,7 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v xml:space="preserve">   - 조회조건: 검색 폼에 표시될 조건들</v>
+        <v xml:space="preserve">   - 옵션: 사용할 공통 옵션 컴포넌트 (쉼표로 구분)</v>
       </c>
     </row>
     <row r="8">
@@ -822,87 +830,132 @@
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>2. 데이터 시트</v>
+        <v>2. 사용 가능한 옵션</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
-        <v xml:space="preserve">   - 첫 번째 행: 화면 제목 (선택사항)</v>
+        <v xml:space="preserve">   - 년월: YearMonthPicker (년월 선택)</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v xml:space="preserve">   - 헤더 행: 그리드 컬럼명 정의</v>
+        <v xml:space="preserve">   - 년: YearPicker (년도 선택)</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v xml:space="preserve">   - 데이터 행: 샘플 데이터 (구조 파악용)</v>
+        <v xml:space="preserve">   - 자재: MaterialSelect (자재/품목 선택)</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v xml:space="preserve">   - 합계 행: "합계", "소계" 등의 키워드 포함 시 자동 인식</v>
+        <v xml:space="preserve">   - 거래처: CustomerSelect (거래처/고객 선택)</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v/>
+        <v xml:space="preserve">   - 부서: DepartmentSelect (부서 선택)</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>3. 조회조건 타입</v>
+        <v xml:space="preserve">   - 계정: AccountSelect (계정과목 선택)</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v xml:space="preserve">   - text: 일반 텍스트 입력</v>
+        <v xml:space="preserve">   - 모델: ModelSelect (모델/제품 선택)</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v xml:space="preserve">   - date: 날짜 선택</v>
+        <v xml:space="preserve">   - 사업장: SiteSelect (사업장 선택)</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v xml:space="preserve">   - combo: 콤보박스 (드롭다운)</v>
+        <v xml:space="preserve">   - 비용: ExpenSelSelect (비용 선택)</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v xml:space="preserve">   - number: 숫자 입력</v>
+        <v/>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v/>
+        <v>3. 그리드컬럼 시트</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>4. 주의사항</v>
+        <v xml:space="preserve">   - Row 1: 화면 제목</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v xml:space="preserve">   - 헤더명은 DB 컬럼과 매핑되므로 정확히 입력</v>
+        <v xml:space="preserve">   - Row 2: 1차 헤더 (그룹 헤더는 셀 병합)</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v xml:space="preserve">   - 숫자 컬럼은 숫자 형식으로 입력</v>
+        <v xml:space="preserve">   - Row 3: 2차 헤더 (상세 컬럼명)</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v xml:space="preserve">   - 날짜는 YYYY-MM-DD 형식 권장</v>
+        <v xml:space="preserve">   - Row 4+: 합계행 ("합계", "소계" 키워드 포함)</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="str">
+        <v>4. 샘플데이터 시트</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="str">
+        <v xml:space="preserve">   - Row 1: 제목</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v xml:space="preserve">   - Row 2: 헤더 (단일 행, 병합 없음)</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v xml:space="preserve">   - Row 3+: 샘플 데이터</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>5. 옵션 사용 예시</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v xml:space="preserve">   - 옵션: 년월, 자재</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v xml:space="preserve">   - 옵션: 년, 거래처, 부서</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:A24"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:A33"/>
   </ignoredErrors>
 </worksheet>
 </file>